--- a/TestData/LV_TMTI0054719_VerificationOfNewFieldAssociatedOpportunityAvailabiltyAndFunctionalityOnCFOpportunityAndEngagementPage.xlsx
+++ b/TestData/LV_TMTI0054719_VerificationOfNewFieldAssociatedOpportunityAvailabiltyAndFunctionalityOnCFOpportunityAndEngagementPage.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B81C0DA4-72F5-4E86-A871-82BECBD60F4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EE439E8-203D-4E60-96F2-417CBD0DF78C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D381DC3E-0C7A-48CF-8E3B-36CB765DCADA}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D381DC3E-0C7A-48CF-8E3B-36CB765DCADA}"/>
   </bookViews>
   <sheets>
     <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>
@@ -275,7 +275,7 @@
     <t>IndustryGroup/HLSector</t>
   </si>
   <si>
-    <t>CSDN-0000007327</t>
+    <t>CSDN-0000002536</t>
   </si>
 </sst>
 </file>
@@ -641,9 +641,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7DDA40C-CB43-498D-A2ED-A0851564593B}">
   <dimension ref="A1:AD2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="4" max="4" width="22.85546875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -735,7 +738,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>29</v>
       </c>
@@ -835,17 +838,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6978B76C-41D6-4CB8-BB5A-CE3CBB65EA6D}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>67</v>
       </c>
@@ -858,22 +861,22 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1988A2C0-E26B-4053-9887-74900EAFFAF5}">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>72</v>
       </c>
@@ -886,13 +889,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28A3F6A9-43ED-49B3-9AC1-A223C8D04358}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>27</v>
       </c>
@@ -900,7 +903,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>73</v>
       </c>
@@ -916,9 +919,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4922F08E-3E13-47AA-BD27-63BC12B6D061}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>47</v>
       </c>
@@ -944,7 +947,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>40</v>
       </c>
@@ -978,22 +981,22 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{825B9F0D-8652-479A-903D-887FA1C2C103}">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>63</v>
       </c>
@@ -1006,23 +1009,23 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81393CD3-5435-4B58-8311-A4C2E7A02EB9}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>75</v>
       </c>

--- a/TestData/LV_TMTI0054719_VerificationOfNewFieldAssociatedOpportunityAvailabiltyAndFunctionalityOnCFOpportunityAndEngagementPage.xlsx
+++ b/TestData/LV_TMTI0054719_VerificationOfNewFieldAssociatedOpportunityAvailabiltyAndFunctionalityOnCFOpportunityAndEngagementPage.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EE439E8-203D-4E60-96F2-417CBD0DF78C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF4D8148-A907-4F5F-A19A-6205B91D1B54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D381DC3E-0C7A-48CF-8E3B-36CB765DCADA}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{D381DC3E-0C7A-48CF-8E3B-36CB765DCADA}"/>
   </bookViews>
   <sheets>
     <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>
@@ -840,7 +840,7 @@
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">

--- a/TestData/LV_TMTI0054719_VerificationOfNewFieldAssociatedOpportunityAvailabiltyAndFunctionalityOnCFOpportunityAndEngagementPage.xlsx
+++ b/TestData/LV_TMTI0054719_VerificationOfNewFieldAssociatedOpportunityAvailabiltyAndFunctionalityOnCFOpportunityAndEngagementPage.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{889E087C-AEED-40F8-B858-F9634BBC5CFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BD5D918-A2E1-4563-8035-C107FE574742}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{D381DC3E-0C7A-48CF-8E3B-36CB765DCADA}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D381DC3E-0C7A-48CF-8E3B-36CB765DCADA}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="2" r:id="rId1"/>
@@ -266,9 +266,6 @@
     <t>James Craven</t>
   </si>
   <si>
-    <t>Gemma Hardy</t>
-  </si>
-  <si>
     <t>Project Amenity</t>
   </si>
   <si>
@@ -276,6 +273,9 @@
   </si>
   <si>
     <t>BUS - Business Services</t>
+  </si>
+  <si>
+    <t>Jennie Stewart</t>
   </si>
 </sst>
 </file>
@@ -1022,13 +1022,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28A3F6A9-43ED-49B3-9AC1-A223C8D04358}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>27</v>
       </c>
@@ -1036,12 +1036,12 @@
         <v>46</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>73</v>
       </c>
       <c r="B2" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -1052,13 +1052,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7DDA40C-CB43-498D-A2ED-A0851564593B}">
   <dimension ref="A1:AD2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="4" width="22.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1069,7 +1069,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>3</v>
@@ -1150,7 +1150,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>29</v>
       </c>
@@ -1161,7 +1161,7 @@
         <v>30</v>
       </c>
       <c r="D2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E2" t="s">
         <v>31</v>
@@ -1250,17 +1250,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6978B76C-41D6-4CB8-BB5A-CE3CBB65EA6D}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>67</v>
       </c>
@@ -1273,22 +1273,22 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1988A2C0-E26B-4053-9887-74900EAFFAF5}">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>72</v>
       </c>
@@ -1301,9 +1301,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4922F08E-3E13-47AA-BD27-63BC12B6D061}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>47</v>
       </c>
@@ -1329,7 +1329,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>40</v>
       </c>
@@ -1363,22 +1363,22 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{825B9F0D-8652-479A-903D-887FA1C2C103}">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>63</v>
       </c>
@@ -1391,25 +1391,25 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81393CD3-5435-4B58-8311-A4C2E7A02EB9}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B3" t="s">
         <v>65</v>
